--- a/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-78,84; 41,65</t>
+          <t>-60,74; 42,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 0,0</t>
+          <t>-80,48; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 24,72</t>
+          <t>-51,66; 25,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,2; 81,34</t>
+          <t>-38,69; 77,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 0,0</t>
+          <t>-63,52; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 17,79</t>
+          <t>-19,31; 18,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 18,79</t>
+          <t>-21,89; 20,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 48,05</t>
+          <t>-21,19; 44,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 21,27</t>
+          <t>-10,71; 21,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 32,52</t>
+          <t>-10,52; 31,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 56,23</t>
+          <t>-6,08; 52,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 16,44</t>
+          <t>-9,33; 14,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 19,49</t>
+          <t>-9,84; 19,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 36,45</t>
+          <t>-7,68; 36,61</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,36; 299,74</t>
+          <t>-79,38; 389,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,79; 483,5</t>
+          <t>-74,7; 511,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 846,51</t>
+          <t>-72,35; 653,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1278,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 247,86</t>
+          <t>-54,21; 224,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 309,63</t>
+          <t>-63,82; 333,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 528,02</t>
+          <t>-55,38; 458,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,27</t>
+          <t>0,0; 73,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,12; 73,29</t>
+          <t>15,8; 68,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,32</t>
+          <t>0,0; 83,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 55,26</t>
+          <t>7,36; 58,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,35</t>
+          <t>0,0; 45,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,97</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 51,53</t>
+          <t>7,47; 51,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,02; 50,02</t>
+          <t>10,32; 50,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,11; 71,84</t>
+          <t>9,61; 73,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 20,88</t>
+          <t>-7,78; 21,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 30,65</t>
+          <t>-3,51; 30,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 47,15</t>
+          <t>-5,67; 41,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 21,64</t>
+          <t>-8,2; 20,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 29,06</t>
+          <t>-6,48; 29,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 44,01</t>
+          <t>-7,64; 38,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,49</t>
+          <t>-4,42; 16,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 23,43</t>
+          <t>-0,94; 24,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 32,18</t>
+          <t>0,4; 33,25</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 625,71</t>
+          <t>-61,76; 629,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 906,0</t>
+          <t>-41,59; 775,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 462,12</t>
+          <t>-47,05; 352,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 449,94</t>
+          <t>-46,07; 475,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 824,56</t>
+          <t>-62,86; 651,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 260,46</t>
+          <t>-31,17; 247,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 356,3</t>
+          <t>-11,46; 360,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 477,27</t>
+          <t>-9,88; 472,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 42,24</t>
+          <t>-60,75; 41,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,48; 0,0</t>
+          <t>-80,85; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 25,48</t>
+          <t>-51,81; 25,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 77,87</t>
+          <t>-28,87; 86,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 0,0</t>
+          <t>-64,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 18,57</t>
+          <t>-16,75; 20,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 20,46</t>
+          <t>-20,11; 17,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 44,32</t>
+          <t>-18,95; 42,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,45</t>
+          <t>-11,06; 21,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 31,77</t>
+          <t>-7,79; 31,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 52,93</t>
+          <t>-8,33; 52,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 14,78</t>
+          <t>-8,98; 15,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 19,3</t>
+          <t>-10,11; 19,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 36,61</t>
+          <t>-5,65; 38,81</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,38; 389,41</t>
+          <t>-72,79; 498,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 441,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 511,66</t>
+          <t>-72,66; 530,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 653,67</t>
+          <t>-63,3; 705,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1123,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,21; 224,33</t>
+          <t>-53,66; 221,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,82; 333,09</t>
+          <t>-60,06; 283,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,38; 458,49</t>
+          <t>-53,88; 480,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,65</t>
+          <t>0,0; 73,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 68,93</t>
+          <t>10,03; 71,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,95</t>
+          <t>0,0; 81,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 58,66</t>
+          <t>7,7; 55,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,36</t>
+          <t>0,0; 56,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 83,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 51,26</t>
+          <t>5,51; 52,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 50,45</t>
+          <t>10,05; 49,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 73,07</t>
+          <t>10,31; 74,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 21,33</t>
+          <t>-9,02; 19,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 30,35</t>
+          <t>-3,29; 31,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 41,03</t>
+          <t>-6,28; 45,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 20,11</t>
+          <t>-7,6; 20,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 29,33</t>
+          <t>-7,92; 26,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 38,87</t>
+          <t>-7,43; 41,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 16,19</t>
+          <t>-4,8; 15,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 24,29</t>
+          <t>-1,65; 24,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 33,25</t>
+          <t>-2,7; 34,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 629,33</t>
+          <t>-66,93; 562,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 775,36</t>
+          <t>-37,11; 952,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1532,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 352,22</t>
+          <t>-46,4; 344,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 475,78</t>
+          <t>-56,42; 418,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 651,79</t>
+          <t>-49,91; 645,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 247,41</t>
+          <t>-34,52; 237,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 360,51</t>
+          <t>-15,38; 346,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 472,79</t>
+          <t>-27,59; 447,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-18,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-39,86</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>35,63</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-18,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>60,14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-39,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,84; 41,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-80,76; 0,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-60,75; 41,86</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,85; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 25,16</t>
+          <t>-62,52; 24,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 86,02</t>
+          <t>-26,2; 81,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 0,0</t>
+          <t>-65,19; 0,0</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-47,04%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>150,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-47,04%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>150,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,99</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,99</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,18</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>13,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 20,44</t>
+          <t>-11,01; 21,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 17,53</t>
+          <t>-9,55; 32,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 42,58</t>
+          <t>-6,6; 60,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 21,15</t>
+          <t>-20,17; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 31,4</t>
+          <t>-20,71; 18,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 52,7</t>
+          <t>-18,84; 51,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 15,17</t>
+          <t>-8,82; 16,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 19,15</t>
+          <t>-9,18; 19,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 38,81</t>
+          <t>-6,27; 40,54</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>190,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,49%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-22,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>163,02%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>104,5%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 498,01</t>
+          <t>-78,79; 483,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 441,29</t>
+          <t>-66,71; 846,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1384,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,66; 530,69</t>
+          <t>-84,36; 299,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 705,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1123,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,66; 221,74</t>
+          <t>-52,31; 247,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,06; 283,28</t>
+          <t>-56,15; 309,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 480,41</t>
+          <t>-52,9; 572,66</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32,4</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>21,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>38,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,16</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,67</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,72</t>
+          <t>40,91</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36,98</t>
+          <t>37,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,16</t>
+          <t>7,18; 55,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 71,52</t>
+          <t>0,0; 46,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,29</t>
+          <t>0,0; 83,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 55,02</t>
+          <t>0,0; 72,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,27</t>
+          <t>10,12; 73,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,97</t>
+          <t>0,0; 85,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 52,04</t>
+          <t>5,78; 51,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 49,0</t>
+          <t>10,02; 50,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 74,43</t>
+          <t>10,47; 72,29</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,96</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14,21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,81</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12,79</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,96</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,95</t>
+          <t>15,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 19,5</t>
+          <t>-7,8; 21,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 31,01</t>
+          <t>-8,19; 29,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 45,9</t>
+          <t>-6,51; 45,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 20,09</t>
+          <t>-7,84; 20,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 26,83</t>
+          <t>-2,99; 30,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 41,92</t>
+          <t>-4,35; 49,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 15,74</t>
+          <t>-4,16; 16,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 24,08</t>
+          <t>-1,7; 23,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 34,41</t>
+          <t>-0,76; 34,46</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>115,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>59,82%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>131,59%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>150,45%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>72,98%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109,29%</t>
+          <t>174,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>124,94%</t>
+          <t>137,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 562,02</t>
+          <t>-45,6; 462,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 952,86</t>
+          <t>-50,28; 449,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1532,13</t>
+          <t>-47,43; 887,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 344,24</t>
+          <t>-65,48; 625,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 418,45</t>
+          <t>-36,55; 906,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 645,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 237,55</t>
+          <t>-29,11; 260,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 346,3</t>
+          <t>-17,47; 356,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 447,08</t>
+          <t>-6,84; 527,77</t>
         </is>
       </c>
     </row>
